--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484354_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484354_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6375</v>
+        <v>3.288</v>
       </c>
       <c r="E2" t="n">
-        <v>2.268</v>
+        <v>1.7824</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3695</v>
+        <v>1.5057</v>
       </c>
       <c r="G2" t="n">
         <v>1.3056</v>
@@ -610,13 +610,13 @@
         <v>1.3674</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5738</v>
+        <v>1.2243</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2217</v>
+        <v>0.7361</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3521</v>
+        <v>0.4883</v>
       </c>
       <c r="V2" t="n">
         <v>-0.6093</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. KIRIS</t>
+          <t>P. CABAÑERO PUERTAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7458</v>
+        <v>2.4548</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0242</v>
+        <v>-0.541</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7216</v>
+        <v>2.9958</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7784</v>
+        <v>0.1097</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1256</v>
+        <v>1.0811</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.3472</v>
+        <v>-0.9714</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6877</v>
+        <v>-0.2045</v>
       </c>
       <c r="K3" t="n">
-        <v>3.955</v>
+        <v>0.4963</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.2673</v>
+        <v>-0.7007</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9093</v>
+        <v>0.3142</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1707</v>
+        <v>0.5848</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.0799</v>
+        <v>-0.2706</v>
       </c>
       <c r="P3" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="Q3" t="n">
         <v>-0.9767</v>
       </c>
-      <c r="Q3" t="n">
-        <v>-3.9069</v>
-      </c>
       <c r="R3" t="n">
-        <v>2.9301</v>
+        <v>2.5395</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8855</v>
+        <v>1.4465</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4116</v>
+        <v>1.0271</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4738</v>
+        <v>0.4194</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9414</v>
+        <v>-0.6642</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8317</v>
+        <v>-0.3869</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.7731</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>M. KIRIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5821</v>
+        <v>1.8226</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2775</v>
+        <v>0.7002</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8596</v>
+        <v>1.1224</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1097</v>
+        <v>1.7784</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0811</v>
+        <v>4.1256</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9714</v>
+        <v>-2.3472</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.2045</v>
+        <v>2.6877</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4963</v>
+        <v>3.955</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.7007</v>
+        <v>-1.2673</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3142</v>
+        <v>-0.9093</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5848</v>
+        <v>0.1707</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2706</v>
+        <v>-1.0799</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5627</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9767</v>
+        <v>-3.9069</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5395</v>
+        <v>2.9301</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5738</v>
+        <v>1.9623</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2906</v>
+        <v>1.0876</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2832</v>
+        <v>0.8747</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6642</v>
+        <v>-0.9414</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3869</v>
+        <v>0.8317</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2772</v>
+        <v>-1.7731</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. POPADIC</t>
+          <t>G. GEORGIOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7169</v>
+        <v>1.2704</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1116</v>
+        <v>-2.7204</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8285</v>
+        <v>3.9908</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4466</v>
+        <v>2.7171</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8491</v>
+        <v>3.6214</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.4025</v>
+        <v>-0.9043</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3409</v>
+        <v>2.1983</v>
       </c>
       <c r="K5" t="n">
-        <v>2.0683</v>
+        <v>2.8319</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.7274</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8943</v>
+        <v>0.5189</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2192</v>
+        <v>0.7895</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6751</v>
+        <v>-0.2706</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-3.3208</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9534</v>
+        <v>-5.8603</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9534</v>
+        <v>2.5395</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2703</v>
+        <v>1.2648</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5009</v>
+        <v>0.3324</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2306</v>
+        <v>0.9325</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. GEORGIOU</t>
+          <t>M. POPADIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.663</v>
+        <v>0.8359</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.8725</v>
+        <v>-0.4556</v>
       </c>
       <c r="F6" t="n">
-        <v>4.5355</v>
+        <v>1.2915</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7171</v>
+        <v>0.4466</v>
       </c>
       <c r="H6" t="n">
-        <v>3.6214</v>
+        <v>1.8491</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9043</v>
+        <v>-1.4025</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1983</v>
+        <v>1.3409</v>
       </c>
       <c r="K6" t="n">
-        <v>2.8319</v>
+        <v>2.0683</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-0.7274</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5189</v>
+        <v>-0.8943</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7895</v>
+        <v>-0.2192</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2706</v>
+        <v>-0.6751</v>
       </c>
       <c r="P6" t="n">
-        <v>-3.3208</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-5.8603</v>
+        <v>-1.9534</v>
       </c>
       <c r="R6" t="n">
-        <v>2.5395</v>
+        <v>1.9534</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6574</v>
+        <v>0.3893</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8198</v>
+        <v>0.1569</v>
       </c>
       <c r="U6" t="n">
-        <v>1.4772</v>
+        <v>0.2324</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1976</v>
+        <v>-0.8803</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8682</v>
+        <v>-0.6054</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3294</v>
+        <v>-0.2749</v>
       </c>
       <c r="G7" t="n">
         <v>-0.189</v>
@@ -1000,13 +1000,13 @@
         <v>0.3907</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1453</v>
+        <v>0.172</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0881</v>
+        <v>0.3508</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2333</v>
+        <v>-0.1789</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2772</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3289</v>
+        <v>-1.1734</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0024</v>
+        <v>0.1035</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3313</v>
+        <v>-1.2769</v>
       </c>
       <c r="G8" t="n">
         <v>-1.1699</v>
@@ -1078,13 +1078,13 @@
         <v>0.9767</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.159</v>
+        <v>-0.0034</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3631</v>
+        <v>-0.262</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2041</v>
+        <v>0.2586</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6025</v>
+        <v>-1.3669</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4279</v>
+        <v>-0.1651</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1746</v>
+        <v>-1.2018</v>
       </c>
       <c r="G9" t="n">
         <v>-1.5767</v>
@@ -1156,13 +1156,13 @@
         <v>1.3674</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1392</v>
+        <v>0.0963</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.4635</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5871</v>
+        <v>0.5598</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2772</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3003</v>
+        <v>-1.7664</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5059</v>
+        <v>-1.1627</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7944</v>
+        <v>-0.6038</v>
       </c>
       <c r="G10" t="n">
         <v>-2.5444</v>
@@ -1234,13 +1234,13 @@
         <v>1.9534</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3103</v>
+        <v>0.2235</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0246</v>
+        <v>0.3186</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2857</v>
+        <v>-0.0951</v>
       </c>
       <c r="V10" t="n">
         <v>0.5545</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5569</v>
+        <v>-1.9152</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1646</v>
+        <v>-2.659</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6076</v>
+        <v>0.7438</v>
       </c>
       <c r="G11" t="n">
         <v>0.9597</v>
@@ -1312,13 +1312,13 @@
         <v>1.5627</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.044</v>
+        <v>0.5977</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3356</v>
+        <v>0.17</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2916</v>
+        <v>0.4277</v>
       </c>
       <c r="V11" t="n">
         <v>-2.1052</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.359099999999999</v>
+        <v>2.569499999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.9336</v>
+        <v>-5.7231</v>
       </c>
       <c r="F12" t="n">
         <v>8.2926</v>
@@ -1372,10 +1372,10 @@
         <v>-6.7389</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.896500000000001</v>
+        <v>-4.8965</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1698000000000003</v>
+        <v>-0.1698000000000001</v>
       </c>
       <c r="O12" t="n">
         <v>-4.7266</v>
@@ -1390,13 +1390,13 @@
         <v>17.5808</v>
       </c>
       <c r="S12" t="n">
-        <v>6.163</v>
+        <v>7.373299999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>2.2435</v>
+        <v>3.454</v>
       </c>
       <c r="U12" t="n">
-        <v>3.9195</v>
+        <v>3.9194</v>
       </c>
       <c r="V12" t="n">
         <v>-3.7107</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.8705</v>
+        <v>5.0995</v>
       </c>
       <c r="E13" t="n">
-        <v>3.7678</v>
+        <v>4.3745</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1027</v>
+        <v>0.725</v>
       </c>
       <c r="G13" t="n">
         <v>0.2666</v>
@@ -1468,13 +1468,13 @@
         <v>2.5395</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.2594</v>
+        <v>-1.0303</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2105</v>
+        <v>-0.6038</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.0489</v>
+        <v>-0.4266</v>
       </c>
       <c r="V13" t="n">
         <v>3.3238</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. TORNÉ DELAURENS</t>
+          <t>O. TOURE JABBY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8853</v>
+        <v>1.2954</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9256</v>
+        <v>-0.0789</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.0403</v>
+        <v>1.3743</v>
       </c>
       <c r="G14" t="n">
-        <v>0.615</v>
+        <v>1.8152</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.3001</v>
+        <v>0.6825</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9151</v>
+        <v>1.1326</v>
       </c>
       <c r="J14" t="n">
-        <v>1.9322</v>
+        <v>1.3654</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5564</v>
+        <v>1.3111</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3758</v>
+        <v>0.0543</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.3172</v>
+        <v>0.4498</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.8565</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5393</v>
+        <v>1.0784</v>
       </c>
       <c r="P14" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3674</v>
+        <v>1.9534</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1216</v>
+        <v>0.1444</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9933999999999999</v>
+        <v>-0.0453</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1281</v>
+        <v>0.1897</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.2186</v>
+        <v>-0.6642</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X14" t="n">
         <v>-1.2186</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>O. TOURE JABBY</t>
+          <t>M. TORNÉ DELAURENS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.879</v>
+        <v>1.2061</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5278</v>
+        <v>1.8134</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3512</v>
+        <v>-0.6072</v>
       </c>
       <c r="G15" t="n">
-        <v>1.8152</v>
+        <v>0.615</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6825</v>
+        <v>-1.3001</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1326</v>
+        <v>1.9151</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3654</v>
+        <v>1.9322</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3111</v>
+        <v>0.5564</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0543</v>
+        <v>1.3758</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4498</v>
+        <v>-1.3172</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-1.8565</v>
       </c>
       <c r="O15" t="n">
-        <v>1.0784</v>
+        <v>0.5393</v>
       </c>
       <c r="P15" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="Q15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-1.9534</v>
-      </c>
       <c r="R15" t="n">
-        <v>1.9534</v>
+        <v>1.3674</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7279</v>
+        <v>0.4423</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5614</v>
+        <v>-0.1189</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1665</v>
+        <v>0.5612</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6642</v>
+        <v>-1.2186</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>-1.2186</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. MURCIANO PUJADAS</t>
+          <t>A. MARTÍN ADELANTADO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1781</v>
+        <v>0.7855</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2237</v>
+        <v>0.463</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4017</v>
+        <v>0.3225</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5301</v>
+        <v>-0.3996</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.0619</v>
+        <v>-1.8432</v>
       </c>
       <c r="I16" t="n">
-        <v>1.592</v>
+        <v>1.4435</v>
       </c>
       <c r="J16" t="n">
-        <v>2.3266</v>
+        <v>0.7779</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0041</v>
+        <v>-0.5308</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3225</v>
+        <v>1.3087</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.7966</v>
+        <v>-1.1775</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.066</v>
+        <v>-1.3123</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2694</v>
+        <v>0.1348</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1953</v>
+        <v>1.5627</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1488</v>
+        <v>1.5627</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3978</v>
+        <v>-0.1004</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5969</v>
+        <v>-0.3149</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9947</v>
+        <v>0.2145</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0549</v>
+        <v>-0.2772</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0549</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. MARTÍN ADELANTADO</t>
+          <t>A. MURCIANO PUJADAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.635</v>
+        <v>0.7603</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6652</v>
+        <v>-0.1226</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0302</v>
+        <v>0.8829</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3996</v>
+        <v>0.5301</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.8432</v>
+        <v>-1.0619</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4435</v>
+        <v>1.592</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7779</v>
+        <v>2.3266</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5308</v>
+        <v>1.0041</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3087</v>
+        <v>1.3225</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1775</v>
+        <v>-1.7966</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3123</v>
+        <v>-2.066</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1348</v>
+        <v>0.2694</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5627</v>
+        <v>2.1488</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2509</v>
+        <v>-0.0199</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1127</v>
+        <v>-0.4958</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1382</v>
+        <v>0.4758</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2772</v>
+        <v>0.0549</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2772</v>
+        <v>0.0549</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. HOMS LORENZO</t>
+          <t>J. JUAREZ GIMENEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1987</v>
+        <v>0.3575</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.4175</v>
+        <v>-1.5192</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2188</v>
+        <v>1.8767</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.9471</v>
+        <v>0.7448</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.2029</v>
+        <v>-2.6954</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2558</v>
+        <v>3.4402</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.9176</v>
+        <v>1.7926</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.3649</v>
+        <v>-1.2433</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5527</v>
+        <v>3.0359</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0295</v>
+        <v>-1.0478</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.838</v>
+        <v>-1.452</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8085</v>
+        <v>0.4043</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="Q18" t="n">
         <v>-2.9301</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7348</v>
+        <v>3.3208</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4936</v>
+        <v>-0.2235</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3798</v>
+        <v>-0.3816</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8734</v>
+        <v>0.1581</v>
       </c>
       <c r="V18" t="n">
-        <v>2.4373</v>
+        <v>-0.5545</v>
       </c>
       <c r="W18" t="n">
-        <v>2.0503</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3869</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. JUAREZ GIMENEZ</t>
+          <t>A. VIÑALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,31 +1891,31 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6471</v>
+        <v>-0.1997</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.227</v>
+        <v>-2.4796</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5798</v>
+        <v>2.2798</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7448</v>
+        <v>-1.4748</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.6954</v>
+        <v>-0.0591</v>
       </c>
       <c r="I19" t="n">
-        <v>3.4402</v>
+        <v>-1.4157</v>
       </c>
       <c r="J19" t="n">
-        <v>1.7926</v>
+        <v>-0.427</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.2433</v>
+        <v>1.3929</v>
       </c>
       <c r="L19" t="n">
-        <v>3.0359</v>
+        <v>-1.82</v>
       </c>
       <c r="M19" t="n">
         <v>-1.0478</v>
@@ -1936,28 +1936,28 @@
         <v>3.3208</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2282</v>
+        <v>-0.3342</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0894</v>
+        <v>-0.341</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1388</v>
+        <v>0.0068</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5545</v>
+        <v>1.2186</v>
       </c>
       <c r="W19" t="n">
+        <v>1.2186</v>
+      </c>
+      <c r="X19" t="n">
         <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>-0.5545</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. VIÑALLONGA GOMEZ</t>
+          <t>C. HOMS LORENZO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5779</v>
+        <v>-0.4074</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.2885</v>
+        <v>-2.9231</v>
       </c>
       <c r="F20" t="n">
-        <v>1.7106</v>
+        <v>2.5157</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.4748</v>
+        <v>-1.9471</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0591</v>
+        <v>-2.2029</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.4157</v>
+        <v>0.2558</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.427</v>
+        <v>-1.9176</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3929</v>
+        <v>-1.3649</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.82</v>
+        <v>-0.5527</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0478</v>
+        <v>-0.0295</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.452</v>
+        <v>-0.838</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4043</v>
+        <v>0.8085</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3907</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q20" t="n">
         <v>-2.9301</v>
       </c>
       <c r="R20" t="n">
-        <v>3.3208</v>
+        <v>2.7348</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.7124</v>
+        <v>-0.7023</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1499</v>
+        <v>-0.1257</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5624</v>
+        <v>-0.5765</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2186</v>
+        <v>2.4373</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2186</v>
+        <v>2.0503</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.3869</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.245</v>
+        <v>-1.8198</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.0151</v>
+        <v>-2.914</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7701</v>
+        <v>1.0942</v>
       </c>
       <c r="G21" t="n">
         <v>0.5183</v>
@@ -2092,13 +2092,13 @@
         <v>0.7814</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2238</v>
+        <v>-0.7986</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8473000000000001</v>
+        <v>-0.7462</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3765</v>
+        <v>-0.0524</v>
       </c>
       <c r="V21" t="n">
         <v>0.6093</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.1382</v>
+        <v>-5.7403</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.0074</v>
+        <v>-4.9062</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1309</v>
+        <v>-0.834</v>
       </c>
       <c r="G22" t="n">
         <v>-2.5056</v>
@@ -2170,13 +2170,13 @@
         <v>0.7814</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.242</v>
+        <v>-0.844</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8473000000000001</v>
+        <v>-0.7462</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3947</v>
+        <v>-0.0978</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2186</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.359000000000002</v>
+        <v>1.3371</v>
       </c>
       <c r="E23" t="n">
-        <v>-8.292799999999998</v>
+        <v>-8.2927</v>
       </c>
       <c r="F23" t="n">
-        <v>6.933499999999999</v>
+        <v>9.629900000000001</v>
       </c>
       <c r="G23" t="n">
         <v>-1.8371</v>
@@ -2221,16 +2221,16 @@
         <v>11.4655</v>
       </c>
       <c r="J23" t="n">
-        <v>4.896500000000001</v>
+        <v>4.8965</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1698999999999999</v>
+        <v>0.1698999999999997</v>
       </c>
       <c r="L23" t="n">
-        <v>4.726500000000001</v>
+        <v>4.7265</v>
       </c>
       <c r="M23" t="n">
-        <v>-6.7338</v>
+        <v>-6.733800000000001</v>
       </c>
       <c r="N23" t="n">
         <v>-13.4725</v>
@@ -2248,13 +2248,13 @@
         <v>20.511</v>
       </c>
       <c r="S23" t="n">
-        <v>-6.162999999999999</v>
+        <v>-3.4665</v>
       </c>
       <c r="T23" t="n">
         <v>-3.9194</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.2436</v>
+        <v>0.4528000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>3.7108</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484354_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484354_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,11 +632,16 @@
       <c r="X2" t="n">
         <v>-0.6093</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484354_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>M. KIRIS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +653,78 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4548</v>
+        <v>1.8226</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.541</v>
+        <v>0.7002</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9958</v>
+        <v>1.1224</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1097</v>
+        <v>1.7784</v>
       </c>
       <c r="H3" t="n">
-        <v>1.0811</v>
+        <v>4.1256</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9714</v>
+        <v>-2.3472</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.2045</v>
+        <v>2.6877</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4963</v>
+        <v>3.955</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.7007</v>
+        <v>-1.2673</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3142</v>
+        <v>-0.9093</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5848</v>
+        <v>0.1707</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2706</v>
+        <v>-1.0799</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5627</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9767</v>
+        <v>-3.9069</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5395</v>
+        <v>2.9301</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4465</v>
+        <v>1.9623</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0271</v>
+        <v>1.0876</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4194</v>
+        <v>0.8747</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.6642</v>
+        <v>-0.9414</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3869</v>
+        <v>0.8317</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2772</v>
+        <v>-1.7731</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484354_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. KIRIS</t>
+          <t>P. CABAÑERO PUERTAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +736,72 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8226</v>
+        <v>1.5279</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7002</v>
+        <v>1.5279</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1224</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7784</v>
+        <v>1.5279</v>
       </c>
       <c r="H4" t="n">
-        <v>4.1256</v>
+        <v>0.921</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.3472</v>
+        <v>0.607</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6877</v>
+        <v>1.5279</v>
       </c>
       <c r="K4" t="n">
-        <v>3.955</v>
+        <v>0.921</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.2673</v>
+        <v>0.607</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9093</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1707</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0799</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.9301</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.9623</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0876</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8747</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9414</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8317</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.7731</v>
+        <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484354_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -861,11 +881,16 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484354_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. POPADIC</t>
+          <t>P. CABANERO PUERTAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8359</v>
+        <v>0.9268999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4556</v>
+        <v>-2.069</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2915</v>
+        <v>2.9958</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4466</v>
+        <v>-1.4182</v>
       </c>
       <c r="H6" t="n">
-        <v>1.8491</v>
+        <v>0.1601</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.4025</v>
+        <v>-1.5784</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3409</v>
+        <v>-1.7324</v>
       </c>
       <c r="K6" t="n">
-        <v>2.0683</v>
+        <v>-0.4247</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7274</v>
+        <v>-1.3077</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8943</v>
+        <v>0.3142</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2192</v>
+        <v>0.5848</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6751</v>
+        <v>-0.2706</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.5627</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9534</v>
+        <v>2.5395</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3893</v>
+        <v>1.4465</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1569</v>
+        <v>1.0271</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2324</v>
+        <v>0.4194</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.3869</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484354_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. FLOREN LARIO</t>
+          <t>M. POPADIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8803</v>
+        <v>0.8359</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6054</v>
+        <v>-0.4556</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2749</v>
+        <v>1.2915</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.189</v>
+        <v>0.4466</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3239</v>
+        <v>1.8491</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1348</v>
+        <v>-1.4025</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0205</v>
+        <v>1.3409</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0205</v>
+        <v>2.0683</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.7274</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2095</v>
+        <v>-0.8943</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3443</v>
+        <v>-0.2192</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1348</v>
+        <v>-0.6751</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.586</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3907</v>
+        <v>1.9534</v>
       </c>
       <c r="S7" t="n">
-        <v>0.172</v>
+        <v>0.3893</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3508</v>
+        <v>0.1569</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1789</v>
+        <v>0.2324</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484354_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. RAMOS SAINZ</t>
+          <t>J. CASTELLO LOGROÑO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1734</v>
+        <v>0.614</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1035</v>
+        <v>0.614</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2769</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1699</v>
+        <v>0.614</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1384</v>
+        <v>0.614</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3083</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1236</v>
+        <v>0.614</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7572</v>
+        <v>0.614</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2935</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6188</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6747</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0034</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.262</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2586</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484354_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. VIDAL RAMOS</t>
+          <t>D. FLOREN LARIO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3669</v>
+        <v>-0.8803</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1651</v>
+        <v>-0.6054</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2018</v>
+        <v>-0.2749</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.5767</v>
+        <v>-0.189</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.5493</v>
+        <v>-0.3239</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0274</v>
+        <v>0.1348</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0565</v>
+        <v>0.0205</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.591</v>
+        <v>0.0205</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6475</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6332</v>
+        <v>-0.2095</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9583</v>
+        <v>-0.3443</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6749000000000001</v>
+        <v>0.1348</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3907</v>
+        <v>-0.586</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3674</v>
+        <v>0.3907</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0963</v>
+        <v>0.172</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4635</v>
+        <v>0.3508</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5598</v>
+        <v>-0.1789</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2772</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.4959</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484354_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. CASADO FAJO</t>
+          <t>P. RAMOS SAINZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7664</v>
+        <v>-1.1734</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1627</v>
+        <v>0.1035</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6038</v>
+        <v>-1.2769</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.5444</v>
+        <v>-1.1699</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6922</v>
+        <v>0.1384</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.2367</v>
+        <v>-1.3083</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3009</v>
+        <v>0.1236</v>
       </c>
       <c r="K10" t="n">
-        <v>1.3955</v>
+        <v>0.7572</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.6964</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2435</v>
+        <v>-1.2935</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7032</v>
+        <v>-0.6188</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5403</v>
+        <v>-0.6747</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9534</v>
+        <v>0.9767</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2235</v>
+        <v>-0.0034</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3186</v>
+        <v>-0.262</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0951</v>
+        <v>0.2586</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.7731</v>
+        <v>1.2186</v>
       </c>
       <c r="X10" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484354_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. CASTELLO LOGROÑO</t>
+          <t>F. VIDAL RAMOS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9152</v>
+        <v>-1.3669</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.659</v>
+        <v>-0.1651</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7438</v>
+        <v>-1.2018</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9597</v>
+        <v>-1.5767</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6091</v>
+        <v>-1.5493</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3506</v>
+        <v>-0.0274</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7653</v>
+        <v>0.0565</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1445</v>
+        <v>-0.591</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6208</v>
+        <v>0.6475</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1944</v>
+        <v>-1.6332</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4646</v>
+        <v>-0.9583</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2702</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.3674</v>
+        <v>0.3907</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5627</v>
+        <v>1.3674</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5977</v>
+        <v>0.0963</v>
       </c>
       <c r="T11" t="n">
-        <v>0.17</v>
+        <v>-0.4635</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4277</v>
+        <v>0.5598</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.1052</v>
+        <v>-0.2772</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6642</v>
+        <v>1.2186</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.441</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484354_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. CASADO FAJO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,229 +1400,240 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.569499999999999</v>
+        <v>-1.7664</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.7231</v>
+        <v>-1.1627</v>
       </c>
       <c r="F12" t="n">
-        <v>8.2926</v>
+        <v>-0.6038</v>
       </c>
       <c r="G12" t="n">
-        <v>1.8371</v>
+        <v>-2.5444</v>
       </c>
       <c r="H12" t="n">
-        <v>13.3026</v>
+        <v>0.6922</v>
       </c>
       <c r="I12" t="n">
-        <v>-11.4657</v>
+        <v>-3.2367</v>
       </c>
       <c r="J12" t="n">
-        <v>6.733700000000001</v>
+        <v>-1.3009</v>
       </c>
       <c r="K12" t="n">
-        <v>13.4727</v>
+        <v>1.3955</v>
       </c>
       <c r="L12" t="n">
-        <v>-6.7389</v>
+        <v>-2.6964</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.8965</v>
+        <v>-1.2435</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1698000000000001</v>
+        <v>-0.7032</v>
       </c>
       <c r="O12" t="n">
-        <v>-4.7266</v>
+        <v>-0.5403</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-20.5109</v>
+        <v>-1.9534</v>
       </c>
       <c r="R12" t="n">
-        <v>17.5808</v>
+        <v>1.9534</v>
       </c>
       <c r="S12" t="n">
-        <v>7.373299999999999</v>
+        <v>0.2235</v>
       </c>
       <c r="T12" t="n">
-        <v>3.454</v>
+        <v>0.3186</v>
       </c>
       <c r="U12" t="n">
-        <v>3.9194</v>
+        <v>-0.0951</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.7107</v>
+        <v>0.5545</v>
       </c>
       <c r="W12" t="n">
-        <v>4.6002</v>
+        <v>1.7731</v>
       </c>
       <c r="X12" t="n">
-        <v>-8.3109</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484354_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>O. HERAS FLECHA</t>
+          <t>J. CASTELLO LOGRONO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>C.B. GRANOLLERS</t>
+          <t>FRIVALCA LA MUELA</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.0995</v>
+        <v>-2.5291</v>
       </c>
       <c r="E13" t="n">
-        <v>4.3745</v>
+        <v>-3.273</v>
       </c>
       <c r="F13" t="n">
-        <v>0.725</v>
+        <v>0.7438</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2666</v>
+        <v>0.3457</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.0537</v>
+        <v>-0.0049</v>
       </c>
       <c r="I13" t="n">
-        <v>2.3204</v>
+        <v>0.3506</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4358</v>
+        <v>0.1514</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6716</v>
+        <v>-0.4694</v>
       </c>
       <c r="L13" t="n">
-        <v>1.1074</v>
+        <v>0.6208</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.1692</v>
+        <v>0.1944</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.3822</v>
+        <v>0.4646</v>
       </c>
       <c r="O13" t="n">
-        <v>1.213</v>
+        <v>-0.2702</v>
       </c>
       <c r="P13" t="n">
-        <v>2.5395</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R13" t="n">
-        <v>2.5395</v>
+        <v>1.5627</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0303</v>
+        <v>0.5977</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6038</v>
+        <v>0.17</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4266</v>
+        <v>0.4277</v>
       </c>
       <c r="V13" t="n">
-        <v>3.3238</v>
+        <v>-2.1052</v>
       </c>
       <c r="W13" t="n">
-        <v>4.5424</v>
+        <v>-0.6642</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.2186</v>
+        <v>-1.441</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484354_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>O. TOURE JABBY</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C.B. GRANOLLERS</t>
+          <t>FRIVALCA LA MUELA</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2954</v>
+        <v>2.569599999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0789</v>
+        <v>-5.7232</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3743</v>
+        <v>8.2926</v>
       </c>
       <c r="G14" t="n">
-        <v>1.8152</v>
+        <v>1.837100000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6825</v>
+        <v>13.3026</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1326</v>
+        <v>-11.4657</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3654</v>
+        <v>6.7338</v>
       </c>
       <c r="K14" t="n">
-        <v>1.3111</v>
+        <v>13.4728</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0543</v>
+        <v>-6.7389</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4498</v>
+        <v>-4.8965</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-0.1698</v>
       </c>
       <c r="O14" t="n">
-        <v>1.0784</v>
+        <v>-4.7266</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9534</v>
+        <v>-20.5109</v>
       </c>
       <c r="R14" t="n">
-        <v>1.9534</v>
+        <v>17.5808</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1444</v>
+        <v>7.373299999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0453</v>
+        <v>3.454</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1897</v>
+        <v>3.9194</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6642</v>
+        <v>-3.7107</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5545</v>
+        <v>4.600199999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2186</v>
-      </c>
+        <v>-8.3109</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. TORNÉ DELAURENS</t>
+          <t>O. HERAS FLECHA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2061</v>
+        <v>5.0995</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8134</v>
+        <v>4.3745</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6072</v>
+        <v>0.725</v>
       </c>
       <c r="G15" t="n">
-        <v>0.615</v>
+        <v>0.2666</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.3001</v>
+        <v>-2.0537</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9151</v>
+        <v>2.3204</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9322</v>
+        <v>0.4358</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5564</v>
+        <v>-0.6716</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3758</v>
+        <v>1.1074</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3172</v>
+        <v>-0.1692</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.8565</v>
+        <v>-1.3822</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5393</v>
+        <v>1.213</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3674</v>
+        <v>2.5395</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3674</v>
+        <v>2.5395</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4423</v>
+        <v>-1.0303</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1189</v>
+        <v>-0.6038</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5612</v>
+        <v>-0.4266</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.2186</v>
+        <v>3.3238</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>4.5424</v>
       </c>
       <c r="X15" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484354_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. MARTÍN ADELANTADO</t>
+          <t>M. TORNÉ DELAURENS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7855</v>
+        <v>1.521</v>
       </c>
       <c r="E16" t="n">
-        <v>0.463</v>
+        <v>1.521</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3225</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3996</v>
+        <v>1.521</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.8432</v>
+        <v>0.307</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4435</v>
+        <v>1.214</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7779</v>
+        <v>1.521</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5308</v>
+        <v>0.307</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3087</v>
+        <v>1.214</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1775</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.3123</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1348</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1004</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3149</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2145</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484354_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. MURCIANO PUJADAS</t>
+          <t>O. TOURE JABBY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7603</v>
+        <v>1.2954</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1226</v>
+        <v>-0.0789</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8829</v>
+        <v>1.3743</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5301</v>
+        <v>1.8152</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0619</v>
+        <v>0.6825</v>
       </c>
       <c r="I17" t="n">
-        <v>1.592</v>
+        <v>1.1326</v>
       </c>
       <c r="J17" t="n">
-        <v>2.3266</v>
+        <v>1.3654</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0041</v>
+        <v>1.3111</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3225</v>
+        <v>0.0543</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.7966</v>
+        <v>0.4498</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.066</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2694</v>
+        <v>1.0784</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1488</v>
+        <v>1.9534</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0199</v>
+        <v>0.1444</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4958</v>
+        <v>-0.0453</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4758</v>
+        <v>0.1897</v>
       </c>
       <c r="V17" t="n">
-        <v>0.0549</v>
+        <v>-0.6642</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0549</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484354_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. JUAREZ GIMENEZ</t>
+          <t>A. VIÑALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3575</v>
+        <v>0.921</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.5192</v>
+        <v>0.921</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8767</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7448</v>
+        <v>0.921</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.6954</v>
+        <v>0.921</v>
       </c>
       <c r="I18" t="n">
-        <v>3.4402</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.7926</v>
+        <v>0.921</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.2433</v>
+        <v>0.921</v>
       </c>
       <c r="L18" t="n">
-        <v>3.0359</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0478</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.452</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4043</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.3208</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2235</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3816</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1581</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484354_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. VIÑALLONGA GOMEZ</t>
+          <t>A. MURCIANO PUJADAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1997</v>
+        <v>0.7603</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.4796</v>
+        <v>-0.1226</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2798</v>
+        <v>0.8829</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4748</v>
+        <v>0.5301</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0591</v>
+        <v>-1.0619</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.4157</v>
+        <v>1.592</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.427</v>
+        <v>2.3266</v>
       </c>
       <c r="K19" t="n">
-        <v>1.3929</v>
+        <v>1.0041</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.82</v>
+        <v>1.3225</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0478</v>
+        <v>-1.7966</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.452</v>
+        <v>-2.066</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4043</v>
+        <v>0.2694</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R19" t="n">
-        <v>3.3208</v>
+        <v>2.1488</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3342</v>
+        <v>-0.0199</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.341</v>
+        <v>-0.4958</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0068</v>
+        <v>0.4758</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2186</v>
+        <v>0.0549</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.0549</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484354_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. HOMS LORENZO</t>
+          <t>A. MARTÍN ADELANTADO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4074</v>
+        <v>0.607</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.9231</v>
+        <v>0.607</v>
       </c>
       <c r="F20" t="n">
-        <v>2.5157</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.9471</v>
+        <v>0.607</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.2029</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2558</v>
+        <v>0.607</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.9176</v>
+        <v>0.607</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.3649</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5527</v>
+        <v>0.607</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0295</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.838</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8085</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.7348</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7023</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1257</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5765</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.0503</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3869</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484354_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. MASPONS MOLINS</t>
+          <t>J. JUAREZ GIMENEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8198</v>
+        <v>0.3575</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.914</v>
+        <v>-1.5192</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0942</v>
+        <v>1.8767</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5183</v>
+        <v>0.7448</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5467</v>
+        <v>-2.6954</v>
       </c>
       <c r="I21" t="n">
-        <v>1.0649</v>
+        <v>3.4402</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8172</v>
+        <v>1.7926</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6958</v>
+        <v>-1.2433</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1214</v>
+        <v>3.0359</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.299</v>
+        <v>-1.0478</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2425</v>
+        <v>-1.452</v>
       </c>
       <c r="O21" t="n">
-        <v>0.9435</v>
+        <v>0.4043</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.1488</v>
+        <v>0.3907</v>
       </c>
       <c r="Q21" t="n">
         <v>-2.9301</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7814</v>
+        <v>3.3208</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7986</v>
+        <v>-0.2235</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7462</v>
+        <v>-0.3816</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0524</v>
+        <v>0.1581</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6093</v>
+        <v>-0.5545</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.0549</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.6642</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484354_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. SALMERON SEGU</t>
+          <t>A. MARTIN ADELANTADO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.7403</v>
+        <v>0.1785</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.9062</v>
+        <v>-0.144</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.834</v>
+        <v>0.3225</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.5056</v>
+        <v>-1.0066</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.2223</v>
+        <v>-1.8432</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2833</v>
+        <v>0.8366</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.2066</v>
+        <v>0.1709</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.9798</v>
+        <v>-0.5308</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2268</v>
+        <v>0.7017</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.299</v>
+        <v>-1.1775</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2425</v>
+        <v>-1.3123</v>
       </c>
       <c r="O22" t="n">
-        <v>0.9435</v>
+        <v>0.1348</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7814</v>
+        <v>1.5627</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.844</v>
+        <v>-0.1004</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7462</v>
+        <v>-0.3149</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0978</v>
+        <v>0.2145</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484354_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. TORNE DELAURENS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,68 +2309,484 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.3371</v>
+        <v>-0.3148</v>
       </c>
       <c r="E23" t="n">
-        <v>-8.2927</v>
+        <v>0.2924</v>
       </c>
       <c r="F23" t="n">
+        <v>-0.6072</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.9059</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-1.6071</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.7010999999999999</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.4113</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.2494</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.1619</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-1.3172</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-1.8565</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.5393</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.4423</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.1189</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.5612</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484354_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>C. HOMS LORENZO</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-0.4074</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-2.9231</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.5157</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-1.9471</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-2.2029</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.2558</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-1.9176</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-1.3649</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-0.5527</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-0.0295</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.838</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.8085</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.7348</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.7023</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.1257</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-0.5765</v>
+      </c>
+      <c r="V24" t="n">
+        <v>2.4373</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.0503</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484354_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A. VINALLONGA GOMEZ</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-1.1207</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-3.4005</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.2798</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-2.3957</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-1.4157</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-1.348</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-1.0478</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-1.452</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.4043</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R25" t="n">
+        <v>3.3208</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.3342</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.341</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.2186</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.2186</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484354_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>I. MASPONS MOLINS</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-1.8198</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-2.914</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.0942</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.5183</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.5467</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.0649</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.8172</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.6958</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.1214</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-0.299</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-1.2425</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.9435</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.7986</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.7462</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.0524</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.6093</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-0.0549</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.6642</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484354_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>M. SALMERON SEGU</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-5.7403</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-4.9062</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0.834</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-2.5056</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-2.2223</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-0.2833</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-2.2066</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-0.9798</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-1.2268</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-0.299</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-1.2425</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.9435</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.844</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.7462</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.0978</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484354_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1.337200000000001</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-8.2926</v>
+      </c>
+      <c r="F28" t="n">
         <v>9.629900000000001</v>
       </c>
-      <c r="G23" t="n">
-        <v>-1.8371</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-13.3028</v>
-      </c>
-      <c r="I23" t="n">
-        <v>11.4655</v>
-      </c>
-      <c r="J23" t="n">
-        <v>4.8965</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0.1698999999999997</v>
-      </c>
-      <c r="L23" t="n">
-        <v>4.7265</v>
-      </c>
-      <c r="M23" t="n">
-        <v>-6.733800000000001</v>
-      </c>
-      <c r="N23" t="n">
+      <c r="G28" t="n">
+        <v>-1.8369</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-13.3027</v>
+      </c>
+      <c r="I28" t="n">
+        <v>11.4656</v>
+      </c>
+      <c r="J28" t="n">
+        <v>4.8966</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.1699999999999997</v>
+      </c>
+      <c r="L28" t="n">
+        <v>4.726599999999999</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-6.7338</v>
+      </c>
+      <c r="N28" t="n">
         <v>-13.4725</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O28" t="n">
         <v>6.739000000000001</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P28" t="n">
         <v>2.9301</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q28" t="n">
         <v>-17.5806</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R28" t="n">
         <v>20.511</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S28" t="n">
         <v>-3.4665</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T28" t="n">
         <v>-3.9194</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U28" t="n">
         <v>0.4528000000000001</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V28" t="n">
         <v>3.7108</v>
       </c>
-      <c r="W23" t="n">
+      <c r="W28" t="n">
         <v>8.3109</v>
       </c>
-      <c r="X23" t="n">
+      <c r="X28" t="n">
         <v>-4.600099999999999</v>
       </c>
+      <c r="Y28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
